--- a/data/trans_dic/P1404-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1404-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>29,16%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,07; 16,33</t>
+          <t>12,26; 16,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,78; 25,41</t>
+          <t>19,6; 24,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,95; 26,78</t>
+          <t>20,78; 26,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,47; 30,23</t>
+          <t>21,94; 28,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,27; 20,71</t>
+          <t>16,33; 20,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,02; 28,92</t>
+          <t>24,06; 28,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,35; 30,29</t>
+          <t>24,5; 30,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>30,36; 35,54</t>
+          <t>29,53; 34,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,99; 17,88</t>
+          <t>14,91; 18,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22,97; 26,61</t>
+          <t>23,08; 26,74</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23,83; 27,96</t>
+          <t>23,65; 27,96</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>28,13; 32,42</t>
+          <t>27,32; 31,25</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,28; 6,41</t>
+          <t>4,27; 6,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,75; 8,23</t>
+          <t>5,75; 8,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,76; 9,05</t>
+          <t>6,64; 8,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,03; 13,05</t>
+          <t>11,25; 14,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,48; 6,86</t>
+          <t>4,47; 6,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,5; 8,11</t>
+          <t>5,47; 8,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,08; 9,64</t>
+          <t>6,93; 9,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,82; 41,15</t>
+          <t>10,43; 12,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,65; 6,28</t>
+          <t>4,65; 6,29</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,06; 7,84</t>
+          <t>6,0; 7,8</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,14; 8,9</t>
+          <t>7,19; 8,84</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,62; 28,34</t>
+          <t>11,08; 12,83</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,1; 6,95</t>
+          <t>3,06; 6,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,01; 10,58</t>
+          <t>5,1; 10,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,13; 11,49</t>
+          <t>5,9; 11,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,26; 14,06</t>
+          <t>9,56; 14,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,61; 6,53</t>
+          <t>2,75; 6,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,38; 6,39</t>
+          <t>2,09; 6,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,26; 8,72</t>
+          <t>4,22; 8,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,98; 14,02</t>
+          <t>10,31; 14,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,34; 6,06</t>
+          <t>3,34; 5,93</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,22; 7,73</t>
+          <t>4,26; 7,66</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,9; 9,35</t>
+          <t>5,71; 9,24</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,25; 13,36</t>
+          <t>10,48; 13,72</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>15,28%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,02; 8,9</t>
+          <t>6,95; 8,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,23; 12,53</t>
+          <t>10,24; 12,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,39; 12,61</t>
+          <t>10,5; 12,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,64; 15,1</t>
+          <t>13,24; 15,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,25; 11,4</t>
+          <t>9,24; 11,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,68; 15,15</t>
+          <t>12,74; 15,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,09; 14,61</t>
+          <t>12,09; 14,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,56; 38,22</t>
+          <t>15,28; 17,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,44; 9,89</t>
+          <t>8,45; 9,83</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,71; 13,43</t>
+          <t>11,83; 13,45</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,57; 13,2</t>
+          <t>11,58; 13,22</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,29; 26,81</t>
+          <t>14,63; 16,04</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>135618</t>
+          <t>143656</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>245059</t>
+          <t>262215</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>380677</t>
+          <t>405871</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>124557; 168455</t>
+          <t>126448; 170939</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>192801; 247690</t>
+          <t>191008; 242639</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>158066; 202025</t>
+          <t>156723; 203074</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>119763; 154241</t>
+          <t>125831; 161580</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>214017; 272422</t>
+          <t>214808; 268101</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>321399; 386891</t>
+          <t>321810; 387672</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>242213; 301329</t>
+          <t>243704; 299605</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>227823; 266656</t>
+          <t>241615; 281519</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>351681; 419643</t>
+          <t>349800; 423644</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>531215; 615440</t>
+          <t>533696; 618349</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>416870; 488999</t>
+          <t>413583; 489020</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>354587; 408683</t>
+          <t>380285; 434934</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>254021</t>
+          <t>278763</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>432853</t>
+          <t>247951</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>686875</t>
+          <t>526715</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>72426; 108599</t>
+          <t>72292; 106999</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>112912; 161543</t>
+          <t>112861; 159864</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>140325; 187954</t>
+          <t>137904; 186192</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>183639; 298442</t>
+          <t>250419; 314371</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>71171; 108966</t>
+          <t>71005; 110350</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>96423; 142254</t>
+          <t>95978; 142021</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>140694; 191650</t>
+          <t>137747; 190140</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>241774; 919345</t>
+          <t>226179; 271900</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>152538; 205948</t>
+          <t>152538; 206404</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>225329; 291535</t>
+          <t>223051; 289872</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>290016; 361954</t>
+          <t>292054; 359149</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>480029; 1281332</t>
+          <t>486853; 563966</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74392</t>
+          <t>83519</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>78240</t>
+          <t>88764</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>152631</t>
+          <t>172283</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17107; 38317</t>
+          <t>16856; 36082</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>24104; 50926</t>
+          <t>24529; 51915</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33542; 62864</t>
+          <t>32259; 61039</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59857; 90909</t>
+          <t>68035; 101678</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>12440; 31100</t>
+          <t>13122; 30431</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10895; 29302</t>
+          <t>9592; 28111</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23368; 47885</t>
+          <t>23167; 49197</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>65867; 92531</t>
+          <t>75649; 105570</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>34292; 62307</t>
+          <t>34343; 60910</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>39658; 72604</t>
+          <t>40008; 72005</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64629; 102512</t>
+          <t>62626; 101322</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>133941; 174627</t>
+          <t>151497; 198274</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>464031</t>
+          <t>505938</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>756152</t>
+          <t>598930</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1220182</t>
+          <t>1104869</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>229997; 291763</t>
+          <t>227814; 290827</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>349739; 428285</t>
+          <t>349907; 427182</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>350813; 425940</t>
+          <t>354641; 428951</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>366353; 520141</t>
+          <t>464903; 543523</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>312640; 385338</t>
+          <t>312230; 383320</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>450398; 538087</t>
+          <t>452390; 535114</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>427143; 515984</t>
+          <t>426977; 516507</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>566969; 1392990</t>
+          <t>568271; 638216</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>561635; 658087</t>
+          <t>562402; 654366</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>815847; 936248</t>
+          <t>824488; 937665</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>799331; 911933</t>
+          <t>800292; 913332</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1012891; 1900234</t>
+          <t>1058061; 1160278</t>
         </is>
       </c>
     </row>
